--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e97cc0d8828a415/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\Work\code\AWS\Aws-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="11_F25DC773A252ABDACC10480E095F44C25BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A109BCD-1075-444B-8064-D88936BF045A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74566518-3BA2-4A11-B5D3-627189D76143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="147">
   <si>
     <t>1st Octate</t>
   </si>
@@ -424,239 +424,75 @@
     <t>Octate</t>
   </si>
   <si>
-    <t>CIDR Block</t>
-  </si>
-  <si>
-    <t>Fixed Bits (Network)</t>
-  </si>
-  <si>
-    <t>Changing Bits (Host)</t>
-  </si>
-  <si>
-    <t>Total IPs (2^(32−X))</t>
-  </si>
-  <si>
-    <t>IP Range Example</t>
-  </si>
-  <si>
-    <t>What It Represents</t>
-  </si>
-  <si>
-    <t>Typical Usage</t>
-  </si>
-  <si>
-    <t>x.x.x.x/32</t>
-  </si>
-  <si>
-    <t>Only the given IP</t>
-  </si>
-  <si>
-    <t>Single machine</t>
-  </si>
-  <si>
-    <t>Allow one IP in Security Group</t>
-  </si>
-  <si>
-    <t>192.168.0.0/30</t>
-  </si>
-  <si>
-    <t>.0 – .3</t>
-  </si>
-  <si>
-    <t>Very small network</t>
-  </si>
-  <si>
-    <t>Point-to-point links</t>
-  </si>
-  <si>
-    <t>192.168.0.0/29</t>
-  </si>
-  <si>
-    <t>.0 – .7</t>
-  </si>
-  <si>
-    <t>Tiny subnet</t>
-  </si>
-  <si>
-    <t>Small internal segments</t>
-  </si>
-  <si>
-    <t>192.168.0.0/28</t>
-  </si>
-  <si>
-    <t>.0 – .15</t>
-  </si>
-  <si>
-    <t>Small subnet</t>
-  </si>
-  <si>
-    <t>Limited hosts</t>
-  </si>
-  <si>
-    <t>192.168.0.0/27</t>
-  </si>
-  <si>
-    <t>.0 – .31</t>
-  </si>
-  <si>
-    <t>Small network</t>
-  </si>
-  <si>
-    <t>Controlled environments</t>
-  </si>
-  <si>
-    <t>192.168.0.0/26</t>
-  </si>
-  <si>
-    <t>.0 – .63</t>
-  </si>
-  <si>
-    <t>Medium-small subnet</t>
-  </si>
-  <si>
-    <t>AWS subnet variants</t>
-  </si>
-  <si>
-    <t>192.168.0.0/25</t>
-  </si>
-  <si>
-    <t>.0 – .127</t>
-  </si>
-  <si>
-    <t>Half /24 network</t>
-  </si>
-  <si>
-    <t>Subnet splitting</t>
-  </si>
-  <si>
-    <t>192.168.0.0/24</t>
-  </si>
-  <si>
-    <t>.0 – .255</t>
-  </si>
-  <si>
-    <t>Small LAN</t>
-  </si>
-  <si>
-    <t>Common AWS subnet</t>
-  </si>
-  <si>
-    <t>192.168.0.0/16</t>
-  </si>
-  <si>
-    <t>192.168.0.0 – 192.168.255.255</t>
-  </si>
-  <si>
-    <t>Medium network</t>
-  </si>
-  <si>
-    <t>VPC-sized networks</t>
-  </si>
-  <si>
-    <t>10.0.0.0/8</t>
-  </si>
-  <si>
-    <t>10.0.0.0 – 10.255.255.255</t>
-  </si>
-  <si>
-    <t>Very large network</t>
-  </si>
-  <si>
-    <t>Enterprise / AWS VPC space</t>
-  </si>
-  <si>
-    <t>0.0.0.0/0</t>
-  </si>
-  <si>
-    <t>4.3 billion</t>
-  </si>
-  <si>
-    <t>Entire IPv4 range</t>
-  </si>
-  <si>
-    <t>All internet</t>
-  </si>
-  <si>
-    <t>Public access rule</t>
-  </si>
-  <si>
-    <t>CIDR</t>
-  </si>
-  <si>
-    <t>What changes</t>
-  </si>
-  <si>
-    <t>Total IPs</t>
-  </si>
-  <si>
-    <t>/32</t>
-  </si>
-  <si>
-    <t>nothing changes</t>
-  </si>
-  <si>
-    <t>1 IP</t>
-  </si>
-  <si>
-    <t>/24</t>
-  </si>
-  <si>
-    <t>last octet changes</t>
-  </si>
-  <si>
-    <t>256 IPs</t>
-  </si>
-  <si>
-    <t>/16</t>
-  </si>
-  <si>
-    <t>last 2 octets change</t>
-  </si>
-  <si>
-    <t>65,536 IPs</t>
-  </si>
-  <si>
-    <t>/8</t>
-  </si>
-  <si>
-    <t>last 3 octets change</t>
-  </si>
-  <si>
-    <t>~16 million IPs</t>
-  </si>
-  <si>
-    <t>/0</t>
-  </si>
-  <si>
-    <t>everything changes</t>
-  </si>
-  <si>
-    <t>all internet</t>
-  </si>
-  <si>
-    <t>Part</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Network portion</t>
-  </si>
-  <si>
-    <t>Identifies the network</t>
-  </si>
-  <si>
-    <t>Host portion</t>
-  </si>
-  <si>
-    <t>Identifies a machine inside the network</t>
+    <t>Subnet Type</t>
+  </si>
+  <si>
+    <t>Route Table</t>
+  </si>
+  <si>
+    <t>Internet Route</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Public RT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.0.0.0/0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Lexend Light"/>
+      </rPr>
+      <t xml:space="preserve"> IGW</t>
+    </r>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Private RT</t>
+  </si>
+  <si>
+    <t>No IGW</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Inside VPC</t>
+  </si>
+  <si>
+    <t>stay local</t>
+  </si>
+  <si>
+    <t>Anywhere else</t>
+  </si>
+  <si>
+    <t>send to internet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,8 +525,14 @@
       <color theme="1"/>
       <name val="Lexend Light"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -703,14 +545,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -733,6 +569,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -743,7 +631,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -763,27 +651,45 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -803,10 +709,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1993,401 +1895,251 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A8431A-05DF-40F3-85DC-6117F5B9D13A}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="32.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B17" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C17" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="B18" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="C18" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="B19" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="10">
-        <v>32</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="C19" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="10">
-        <v>30</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8">
-        <v>4</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="10">
-        <v>29</v>
-      </c>
-      <c r="C4" s="8">
-        <v>3</v>
-      </c>
-      <c r="D4" s="8">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="10">
-        <v>28</v>
-      </c>
-      <c r="C5" s="8">
-        <v>4</v>
-      </c>
-      <c r="D5" s="8">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="10">
-        <v>27</v>
-      </c>
-      <c r="C6" s="8">
-        <v>5</v>
-      </c>
-      <c r="D6" s="8">
-        <v>32</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="10">
-        <v>26</v>
-      </c>
-      <c r="C7" s="8">
-        <v>6</v>
-      </c>
-      <c r="D7" s="8">
-        <v>64</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="10">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8">
-        <v>128</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="10">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8">
-        <v>8</v>
-      </c>
-      <c r="D9" s="8">
-        <v>256</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B10" s="10">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8">
-        <v>16</v>
-      </c>
-      <c r="D10" s="9">
-        <v>65536</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="10">
-        <v>8</v>
-      </c>
-      <c r="C11" s="8">
-        <v>24</v>
-      </c>
-      <c r="D11" s="9">
-        <v>16777216</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8">
-        <v>32</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
     </row>
     <row r="21" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>198</v>
-      </c>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-    </row>
-    <row r="27" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17"/>
+      <c r="B28" s="18"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18"/>
+    </row>
+    <row r="30" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\Work\code\AWS\Aws-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74566518-3BA2-4A11-B5D3-627189D76143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9205A1-AB2C-4598-B13E-866959DBA817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="152">
   <si>
     <t>1st Octate</t>
   </si>
@@ -470,22 +470,37 @@
     <t>No IGW</t>
   </si>
   <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Inside VPC</t>
-  </si>
-  <si>
-    <t>stay local</t>
-  </si>
-  <si>
-    <t>Anywhere else</t>
-  </si>
-  <si>
-    <t>send to internet</t>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>NAT Instance</t>
+  </si>
+  <si>
+    <t>Traffic translator</t>
+  </si>
+  <si>
+    <t>Public Subnet</t>
+  </si>
+  <si>
+    <t>Internet reachability</t>
+  </si>
+  <si>
+    <t>Elastic IP</t>
+  </si>
+  <si>
+    <t>Stable public identity</t>
+  </si>
+  <si>
+    <t>Redirect private traffic</t>
+  </si>
+  <si>
+    <t>IGW</t>
+  </si>
+  <si>
+    <t>Internet access</t>
   </si>
 </sst>
 </file>
@@ -1948,8 +1963,12 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -1957,8 +1976,12 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>149</v>
+      </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -1966,8 +1989,12 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>151</v>
+      </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\Work\code\AWS\Aws-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9205A1-AB2C-4598-B13E-866959DBA817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1EC86-5F7E-4500-8746-A74553DCE879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
     <t>1st Octate</t>
   </si>
@@ -470,37 +470,43 @@
     <t>No IGW</t>
   </si>
   <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>NAT Instance</t>
-  </si>
-  <si>
-    <t>Traffic translator</t>
-  </si>
-  <si>
-    <t>Public Subnet</t>
-  </si>
-  <si>
-    <t>Internet reachability</t>
-  </si>
-  <si>
-    <t>Elastic IP</t>
-  </si>
-  <si>
-    <t>Stable public identity</t>
-  </si>
-  <si>
-    <t>Redirect private traffic</t>
-  </si>
-  <si>
-    <t>IGW</t>
-  </si>
-  <si>
-    <t>Internet access</t>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>High Resiliency</t>
+  </si>
+  <si>
+    <t>Maximum Resiliency</t>
+  </si>
+  <si>
+    <t>Total Connections</t>
+  </si>
+  <si>
+    <t>Locations</t>
+  </si>
+  <si>
+    <t>2 (1 connection each)</t>
+  </si>
+  <si>
+    <t>2 (2 connections each)</t>
+  </si>
+  <si>
+    <t>Device Redundancy</t>
+  </si>
+  <si>
+    <t>Per location</t>
+  </si>
+  <si>
+    <t>Per location + per device</t>
+  </si>
+  <si>
+    <t>Exam Trigger</t>
+  </si>
+  <si>
+    <t>"High availability/Resiliency"</t>
+  </si>
+  <si>
+    <t>"Maximum Resiliency"</t>
   </si>
 </sst>
 </file>
@@ -1913,13 +1919,13 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="10" customWidth="1"/>
     <col min="2" max="2" width="38.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="32.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="10" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
@@ -1930,7 +1936,9 @@
       <c r="B1" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="9"/>
+      <c r="C1" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
@@ -1938,12 +1946,14 @@
     </row>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="11"/>
+      <c r="B2" s="11">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11">
+        <v>4</v>
+      </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
@@ -1956,7 +1966,9 @@
       <c r="B3" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="11"/>
+      <c r="C3" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
@@ -1964,12 +1976,14 @@
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="11"/>
+        <v>149</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -1977,24 +1991,22 @@
     </row>
     <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>153</v>
+      </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>151</v>
-      </c>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\Work\code\AWS\Aws-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1EC86-5F7E-4500-8746-A74553DCE879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20191283-B605-411F-A578-D74A8A21B55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>1st Octate</t>
   </si>
@@ -470,43 +470,40 @@
     <t>No IGW</t>
   </si>
   <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>High Resiliency</t>
-  </si>
-  <si>
-    <t>Maximum Resiliency</t>
-  </si>
-  <si>
-    <t>Total Connections</t>
-  </si>
-  <si>
-    <t>Locations</t>
-  </si>
-  <si>
-    <t>2 (1 connection each)</t>
-  </si>
-  <si>
-    <t>2 (2 connections each)</t>
-  </si>
-  <si>
-    <t>Device Redundancy</t>
-  </si>
-  <si>
-    <t>Per location</t>
-  </si>
-  <si>
-    <t>Per location + per device</t>
-  </si>
-  <si>
-    <t>Exam Trigger</t>
-  </si>
-  <si>
-    <t>"High availability/Resiliency"</t>
-  </si>
-  <si>
-    <t>"Maximum Resiliency"</t>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Customer Gateway (CGW)</t>
+  </si>
+  <si>
+    <t>On-premises</t>
+  </si>
+  <si>
+    <t>Represents your on-prem router/VPN device</t>
+  </si>
+  <si>
+    <t>Virtual Private Gateway (VGW)</t>
+  </si>
+  <si>
+    <t>AWS side</t>
+  </si>
+  <si>
+    <t>VPN endpoint attached to VPC</t>
+  </si>
+  <si>
+    <t>Site-to-Site VPN Connection</t>
+  </si>
+  <si>
+    <t>Between CGW &amp; VGW</t>
+  </si>
+  <si>
+    <t>The actual VPN tunnel</t>
   </si>
 </sst>
 </file>
@@ -1919,8 +1916,8 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="10" customWidth="1"/>
-    <col min="2" max="2" width="38.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" style="10" customWidth="1"/>
     <col min="3" max="3" width="44.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" style="10" bestFit="1" customWidth="1"/>
@@ -1948,11 +1945,11 @@
       <c r="A2" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="11">
-        <v>2</v>
-      </c>
-      <c r="C2" s="11">
-        <v>4</v>
+      <c r="B2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>146</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -1961,13 +1958,13 @@
     </row>
     <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -1976,13 +1973,13 @@
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -1990,15 +1987,9 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>153</v>
-      </c>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>

--- a/Temp.xlsx
+++ b/Temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\Work\code\AWS\Aws-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20191283-B605-411F-A578-D74A8A21B55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84B9D99-A3CC-4E08-B7E8-AA36BF4FEACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="153">
   <si>
     <t>1st Octate</t>
   </si>
@@ -470,40 +470,40 @@
     <t>No IGW</t>
   </si>
   <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Customer Gateway (CGW)</t>
-  </si>
-  <si>
-    <t>On-premises</t>
-  </si>
-  <si>
-    <t>Represents your on-prem router/VPN device</t>
-  </si>
-  <si>
-    <t>Virtual Private Gateway (VGW)</t>
-  </si>
-  <si>
-    <t>AWS side</t>
-  </si>
-  <si>
-    <t>VPN endpoint attached to VPC</t>
-  </si>
-  <si>
-    <t>Site-to-Site VPN Connection</t>
-  </si>
-  <si>
-    <t>Between CGW &amp; VGW</t>
-  </si>
-  <si>
-    <t>The actual VPN tunnel</t>
+    <t>Characteristic</t>
+  </si>
+  <si>
+    <t>Dedicated Instances</t>
+  </si>
+  <si>
+    <t>Dedicated Hosts</t>
+  </si>
+  <si>
+    <t>Enables the use of dedicated physical servers</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>Per instance billing (subject to a $2 per region fee)</t>
+  </si>
+  <si>
+    <t>Per host billing</t>
+  </si>
+  <si>
+    <t>Visibility of sockets, cores, host ID</t>
+  </si>
+  <si>
+    <t>Affinity between a host and instance</t>
+  </si>
+  <si>
+    <t>Targeted instance placement</t>
+  </si>
+  <si>
+    <t>Automatic instance placement</t>
+  </si>
+  <si>
+    <t>Add capacity using an allocation request</t>
   </si>
 </sst>
 </file>
@@ -1916,9 +1916,9 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="10" customWidth="1"/>
@@ -1949,7 +1949,7 @@
         <v>145</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -1958,14 +1958,12 @@
     </row>
     <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>149</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
@@ -1973,13 +1971,11 @@
     </row>
     <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>151</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -1987,45 +1983,67 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
+      <c r="A5" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
+      <c r="C5" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
+      <c r="A6" s="11" t="s">
+        <v>149</v>
+      </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+      <c r="A7" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="C7" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="A8" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+      <c r="A9" s="11" t="s">
+        <v>152</v>
+      </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
